--- a/Asegurados_SIS/Data/Asegurados_Por_Microrred.xlsx
+++ b/Asegurados_SIS/Data/Asegurados_Por_Microrred.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\proyectos_python\DashboardExcel\Asegurados_SIS\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB501992-8A86-4F4C-BF43-C76F5C54D54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35458A7F-C1FE-4D4F-AE5E-4FC8B7816B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12336" xr2:uid="{572A1543-5C28-4FF2-A82D-7E6B707BD919}"/>
+    <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12336" xr2:uid="{A087E504-FFE4-44E9-B3EA-F257F47BC42E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -931,7 +931,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8975F646-D5DC-450A-B67F-A2C0ABEF2B8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96E06F50-4118-4ACB-AB72-C7F4456CD985}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
   <cols>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>17864</v>
+        <v>17914</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -971,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>17038</v>
+        <v>17095</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -982,7 +982,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>16454</v>
+        <v>16292</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -993,7 +993,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>12611</v>
+        <v>12592</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="1">
-        <v>12429</v>
+        <v>12379</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>11449</v>
+        <v>11348</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1026,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="1">
-        <v>10620</v>
+        <v>10601</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1037,7 +1037,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="1">
-        <v>7682</v>
+        <v>7639</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1048,7 +1048,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="1">
-        <v>6452</v>
+        <v>6447</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1059,7 +1059,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="1">
-        <v>6361</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1070,7 +1070,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="1">
-        <v>6267</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1081,7 +1081,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="1">
-        <v>6166</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1092,7 +1092,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="1">
-        <v>4633</v>
+        <v>4640</v>
       </c>
     </row>
   </sheetData>
